--- a/data/trans_dic/IP19C09-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C09-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por otros motivos</t>
+          <t>Menores que en su última visita al dentista fue por otros motivos (tasa de respuesta: 97,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 10,0</t>
+          <t>0,97; 9,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 5,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,21</t>
+          <t>1,1; 11,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,63</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,02</t>
+          <t>0,0; 8,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,17</t>
+          <t>0,0; 5,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,77</t>
+          <t>0,93; 5,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,58</t>
+          <t>0,57; 5,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 6,4</t>
+          <t>0,78; 6,04</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,08</t>
+          <t>0,63; 5,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,78</t>
+          <t>1,17; 6,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,72</t>
+          <t>0,61; 5,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,76</t>
+          <t>0,6; 5,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,56</t>
+          <t>0,59; 5,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,59</t>
+          <t>0,61; 3,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,46</t>
+          <t>1,11; 4,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,2</t>
+          <t>1,19; 4,94</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,03</t>
+          <t>0,0; 4,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,54</t>
+          <t>0,0; 4,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,71</t>
+          <t>0,62; 6,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,78</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,75</t>
+          <t>0,0; 4,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,93</t>
+          <t>0,43; 4,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,52</t>
+          <t>0,0; 3,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,85</t>
+          <t>0,0; 5,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,84</t>
+          <t>0,67; 6,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 11,06</t>
+          <t>2,7; 11,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 9,05</t>
+          <t>1,92; 9,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,96</t>
+          <t>1,67; 5,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,1</t>
+          <t>0,4; 3,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,24</t>
+          <t>1,6; 6,16</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,67</t>
+          <t>0,64; 2,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,94</t>
+          <t>0,73; 3,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,1</t>
+          <t>1,37; 4,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,98</t>
+          <t>1,83; 4,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,52</t>
+          <t>0,84; 3,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,11</t>
+          <t>1,34; 4,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,32</t>
+          <t>1,44; 3,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,74</t>
+          <t>1,0; 2,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,55</t>
+          <t>1,66; 3,63</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por otros motivos (tasa de respuesta: 97,59%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3010</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2592</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4273</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3237</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3440</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>734; 7104</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4185</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>721; 7520</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4443</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6329</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3749</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1464; 9083</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>843; 8114</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1080; 8393</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3145</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2718</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2648</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2549</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3298</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5251</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2884</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>694; 6314</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1196; 7121</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>680; 6151</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>671; 6118</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>625; 5855</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1349; 7572</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2483; 9686</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2478; 10260</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1774</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1241</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2831</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3438</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>484; 4716</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3302</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3555</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>638; 6222</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3489</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4261</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2448</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4635</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6005</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3083</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>7083</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3364</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5323</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>713; 6630</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2430; 9991</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4187</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2011; 10069</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3105; 10970</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>741; 7244</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3367; 12957</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4893</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5648</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>8842</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11090</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6576</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>15982</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>12224</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>17458</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2232; 10004</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2516; 11014</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4764; 14960</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6609; 17076</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3037; 12290</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4781; 15423</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10249; 22854</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>7098; 19184</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>11667; 25541</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C09-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C09-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 9,39</t>
+          <t>0,98; 9,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 6,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 11,47</t>
+          <t>1,1; 10,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 5,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,59</t>
+          <t>0,0; 8,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,1</t>
+          <t>0,0; 7,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,75</t>
+          <t>1,16; 5,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,5</t>
+          <t>0,58; 5,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,04</t>
+          <t>0,79; 5,66</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,7</t>
+          <t>0,55; 5,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,96</t>
+          <t>1,22; 6,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,51</t>
+          <t>0,61; 6,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,46</t>
+          <t>0,6; 5,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,57</t>
+          <t>0,65; 6,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,42</t>
+          <t>0,57; 3,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,35</t>
+          <t>0,89; 4,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,94</t>
+          <t>1,24; 4,84</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,09</t>
+          <t>0,0; 4,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,37 +908,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,68</t>
+          <t>0,0; 5,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,06</t>
+          <t>0,63; 6,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,86</t>
+          <t>0,0; 4,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,23</t>
+          <t>0,43; 4,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,5</t>
+          <t>0,0; 4,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,37 +1018,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,27</t>
+          <t>0,68; 6,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 11,1</t>
+          <t>2,8; 10,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 9,63</t>
+          <t>1,61; 8,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,9</t>
+          <t>1,47; 5,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,89</t>
+          <t>0,41; 4,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,16</t>
+          <t>1,69; 6,16</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,85</t>
+          <t>0,55; 2,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,18</t>
+          <t>0,77; 3,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,31</t>
+          <t>1,41; 4,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,72</t>
+          <t>1,93; 4,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,41</t>
+          <t>0,87; 3,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,33</t>
+          <t>1,32; 4,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,21</t>
+          <t>1,47; 3,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,71</t>
+          <t>1,0; 2,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,63</t>
+          <t>1,62; 3,58</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>734; 7104</t>
+          <t>743; 7441</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4185</t>
+          <t>0; 4559</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>721; 7520</t>
+          <t>723; 7070</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4443</t>
+          <t>0; 4916</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6329</t>
+          <t>0; 6499</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3749</t>
+          <t>0; 5218</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1464; 9083</t>
+          <t>1825; 9117</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>843; 8114</t>
+          <t>852; 8069</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1080; 8393</t>
+          <t>1092; 7870</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2884</t>
+          <t>0; 3087</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>694; 6314</t>
+          <t>614; 6488</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1196; 7121</t>
+          <t>1252; 6911</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>680; 6151</t>
+          <t>682; 6791</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>671; 6118</t>
+          <t>670; 6021</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>625; 5855</t>
+          <t>687; 6505</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1349; 7572</t>
+          <t>1262; 6979</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2483; 9686</t>
+          <t>1994; 9146</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2478; 10260</t>
+          <t>2572; 10036</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2831</t>
+          <t>0; 3149</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1753,37 +1753,37 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3438</t>
+          <t>0; 3685</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>484; 4716</t>
+          <t>491; 5116</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3302</t>
+          <t>0; 3335</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3555</t>
+          <t>0; 3394</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>638; 6222</t>
+          <t>635; 5908</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3489</t>
+          <t>0; 3292</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4261</t>
+          <t>0; 4411</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3364</t>
+          <t>0; 4054</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5323</t>
+          <t>0; 5321</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>713; 6630</t>
+          <t>719; 6602</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2430; 9991</t>
+          <t>2517; 9698</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4187</t>
+          <t>0; 4302</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2011; 10069</t>
+          <t>1683; 9223</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3105; 10970</t>
+          <t>2737; 10727</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>741; 7244</t>
+          <t>762; 7470</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3367; 12957</t>
+          <t>3547; 12960</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2232; 10004</t>
+          <t>1936; 9331</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2516; 11014</t>
+          <t>2675; 11731</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4764; 14960</t>
+          <t>4889; 14753</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6609; 17076</t>
+          <t>6994; 17441</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3037; 12290</t>
+          <t>3127; 12029</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4781; 15423</t>
+          <t>4692; 15426</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10249; 22854</t>
+          <t>10510; 23692</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7098; 19184</t>
+          <t>7083; 19105</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11667; 25541</t>
+          <t>11418; 25186</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C09-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C09-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,98%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,8%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,95%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,83</t>
+          <t>0,0; 4,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,17</t>
+          <t>0,0; 10,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,78</t>
+          <t>0,0; 5,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,98</t>
+          <t>0,99; 10,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,83</t>
+          <t>0,0; 5,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,1</t>
+          <t>1,1; 10,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,78</t>
+          <t>1,04; 5,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,47</t>
+          <t>0,57; 5,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,66</t>
+          <t>0,56; 6,4</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2,35%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,07%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,61; 6,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,86</t>
+          <t>0,6; 5,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 6,75</t>
+          <t>0,6; 5,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,93</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>0,61; 6,08</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,6; 5,37</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,19</t>
+          <t>1,15; 6,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,15</t>
+          <t>0,57; 3,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,1</t>
+          <t>1,15; 4,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,84</t>
+          <t>1,47; 5,2</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,37 +898,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,55</t>
+          <t>0,62; 6,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 4,78</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,75</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,03</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,01</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,63; 6,57</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,21</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,64</t>
+          <t>0,0; 4,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,02</t>
+          <t>0,43; 3,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1,89%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,32%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,22</t>
+          <t>2,86; 11,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 4,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,24</t>
+          <t>1,91; 9,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 10,77</t>
+          <t>0,0; 3,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 8,82</t>
+          <t>0,68; 5,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,77</t>
+          <t>1,46; 5,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,01</t>
+          <t>0,39; 4,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,16</t>
+          <t>1,56; 6,24</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,66</t>
+          <t>1,97; 4,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,39</t>
+          <t>0,82; 3,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,25</t>
+          <t>1,22; 4,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,82</t>
+          <t>0,58; 2,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,34</t>
+          <t>0,72; 2,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,33</t>
+          <t>1,2; 4,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,32</t>
+          <t>1,5; 3,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,7</t>
+          <t>1,05; 2,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,58</t>
+          <t>1,62; 3,55</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>3010</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1331</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2592</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1263</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1906</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>848</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>743; 7441</t>
+          <t>0; 3807</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4559</t>
+          <t>0; 7377</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>723; 7070</t>
+          <t>0; 3802</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4916</t>
+          <t>746; 7571</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6499</t>
+          <t>0; 4342</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5218</t>
+          <t>722; 6695</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1825; 9117</t>
+          <t>1640; 9109</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>852; 8069</t>
+          <t>843; 8234</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1092; 7870</t>
+          <t>782; 8898</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2718</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2648</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2549</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>580</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2603</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3145</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2718</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2648</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2549</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3087</t>
+          <t>682; 7505</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>614; 6488</t>
+          <t>671; 6461</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1252; 6911</t>
+          <t>633; 5846</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>682; 6791</t>
+          <t>0; 3219</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>670; 6021</t>
+          <t>671; 6730</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>687; 6505</t>
+          <t>1181; 6942</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1262; 6979</t>
+          <t>1269; 7953</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1994; 9146</t>
+          <t>2560; 9931</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2572; 10036</t>
+          <t>3054; 10798</t>
         </is>
       </c>
     </row>
@@ -1637,27 +1637,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1774</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>657</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1774</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3149</t>
+          <t>486; 5223</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0; 3780</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2742</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4174</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3685</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>491; 5116</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3335</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3394</t>
+          <t>0; 3337</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>635; 5908</t>
+          <t>633; 5787</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3292</t>
+          <t>0; 3296</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4411</t>
+          <t>0; 4345</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4635</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>671</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1714</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2448</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5335</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1369</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4635</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4054</t>
+          <t>2572; 9963</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5321</t>
+          <t>0; 4132</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>719; 6602</t>
+          <t>1993; 9462</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2517; 9698</t>
+          <t>0; 3376</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4302</t>
+          <t>0; 6211</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1683; 9223</t>
+          <t>718; 6170</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2737; 10727</t>
+          <t>2720; 11080</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>762; 7470</t>
+          <t>728; 7641</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3547; 12960</t>
+          <t>3271; 13113</t>
         </is>
       </c>
     </row>
@@ -1963,27 +1963,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>11090</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6576</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>4893</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>5648</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>8842</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>11090</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6576</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8616</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1936; 9331</t>
+          <t>7123; 18017</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2675; 11731</t>
+          <t>2946; 12686</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4889; 14753</t>
+          <t>4364; 14639</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6994; 17441</t>
+          <t>2049; 9353</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3127; 12029</t>
+          <t>2479; 10202</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4692; 15426</t>
+          <t>4151; 14237</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10510; 23692</t>
+          <t>10666; 23660</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7083; 19105</t>
+          <t>7409; 19371</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11418; 25186</t>
+          <t>11379; 24982</t>
         </is>
       </c>
     </row>
